--- a/output/Master_BOQ_Verification.xlsx
+++ b/output/Master_BOQ_Verification.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Master Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Detailed BOQ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Nesting by Material" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="QC Audit Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +81,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +124,12 @@
         <bgColor rgb="000284C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D97706"/>
+        <bgColor rgb="00D97706"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -158,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,14 +203,14 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +219,9 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,17 +588,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="88.5" customWidth="1" min="2" max="2"/>
     <col width="49.5" customWidth="1" min="3" max="3"/>
-    <col width="54.5" customWidth="1" min="4" max="4"/>
+    <col width="109.5" customWidth="1" min="4" max="4"/>
     <col width="26.5" customWidth="1" min="5" max="5"/>
     <col width="24.5" customWidth="1" min="6" max="6"/>
     <col width="23.5" customWidth="1" min="7" max="7"/>
-    <col width="21.5" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="26.5" customWidth="1" min="9" max="9"/>
     <col width="25.5" customWidth="1" min="10" max="10"/>
   </cols>
@@ -604,7 +614,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated by Antigravity AEC Batch Takeoff &amp; Global Nesting Engine | 2026-10-22 07:39</t>
+          <t>Generated by Antigravity AEC Batch Takeoff &amp; Global Nesting Engine | 2026-10-22 21:57</t>
         </is>
       </c>
     </row>
@@ -618,21 +628,21 @@
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>TOTAL NET ACOUSTIC AREA
-62.33 m²</t>
+80.85 m²</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>TOTAL PANELS / TILES
-39 pcs</t>
+44 pcs</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>TOTAL STOCK SHEETS REQ.
-27 sheets</t>
+29 sheets</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
@@ -699,21 +709,21 @@
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>OVERALL MATERIAL YIELD
-50.0%</t>
+51.3%</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SCRAP / OFFCUT WASTE
-50.0%</t>
+48.7%</t>
         </is>
       </c>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>ESTIMATED SHEET COST
-$2,080.00</t>
+$1,924.00</t>
         </is>
       </c>
       <c r="J9" s="5" t="n"/>
@@ -825,285 +835,316 @@
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Fabric Wrapped 25mm</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>8.494</v>
+        <v>30.771</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11.52</v>
+        <v>17.28</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.7373263888888889</v>
+        <v>1.780723379629629</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>0.2626736111111111</v>
+        <v>0</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>87.75</v>
+        <v>65</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>23.008</v>
+        <v>46.098</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>48.96</v>
+        <v>60.48</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.4699407679738563</v>
+        <v>0.7621941137566138</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>0.5300592320261437</v>
+        <v>0.2378058862433862</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>65</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>1105</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="9" t="inlineStr">
         <is>
+          <t>Polyester 9mm</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.7778472222222224</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0.2221527777777776</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
           <t>Wood Slat Panel</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>30.827</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>1.78396412037037</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13" t="n">
+      <c r="C20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="I20" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="J19" s="13" t="n">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="19" t="inlineStr">
+      <c r="J20" s="18" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROJECT SCOPE</t>
         </is>
       </c>
-      <c r="C20" s="19">
-        <f>SUM(C17:C19)</f>
+      <c r="C21" s="19">
+        <f>SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D20" s="20">
-        <f>SUM(D17:D19)</f>
+      <c r="D21" s="20">
+        <f>SUM(D17:D20)</f>
         <v/>
       </c>
-      <c r="E20" s="19">
-        <f>SUM(E17:E19)</f>
+      <c r="E21" s="19">
+        <f>SUM(E17:E20)</f>
         <v/>
       </c>
-      <c r="F20" s="20">
-        <f>SUM(F17:F19)</f>
+      <c r="F21" s="20">
+        <f>SUM(F17:F20)</f>
         <v/>
       </c>
-      <c r="G20" s="21">
-        <f>D20/F20</f>
+      <c r="G21" s="21">
+        <f>D21/F21</f>
         <v/>
       </c>
-      <c r="H20" s="21">
-        <f>1-G20</f>
+      <c r="H21" s="21">
+        <f>1-G21</f>
         <v/>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="23">
-        <f>SUM(J17:J19)</f>
+      <c r="J21" s="23">
+        <f>SUM(J17:J20)</f>
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22"/>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>2. PAGE-BY-PAGE DRAWING TAKEOFF SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="24" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Page No.</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Drawing / Room Name</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>Materials Present</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>Panel Count</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>Gross Area (m²)</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>Cutout Area (m²)</t>
         </is>
       </c>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>Net Area (m²)</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>% of Project Net Area</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="25" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>Polyester 9mm, Wood Slat Panel</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>35.099</v>
-      </c>
-      <c r="G26" s="16" t="n">
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel, AP-1: Polyester 9mm Acoustic Panel, Polyester 9mm, Wood Slat Panel</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>46.348</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H26" s="16" t="n">
-        <v>34.539</v>
-      </c>
-      <c r="I26" s="17" t="n">
-        <v>0.554141731778145</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="27" t="inlineStr">
+      <c r="H27" s="11" t="n">
+        <v>45.788</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0.5663281839433032</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Fabric Wrapped 25mm, Polyester 9mm, Wood Slat Panel</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>28.562</v>
-      </c>
-      <c r="G27" s="11" t="n">
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel, AP-1: Polyester 9mm Acoustic Panel</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>35.834</v>
+      </c>
+      <c r="G28" s="16" t="n">
         <v>0.772</v>
       </c>
-      <c r="H27" s="11" t="n">
-        <v>27.79</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>0.4458614770010749</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="H28" s="16" t="n">
+        <v>35.063</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0.4336718160566969</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E28" s="19">
-        <f>SUM(E26:E27)</f>
+      <c r="E29" s="19">
+        <f>SUM(E27:E28)</f>
         <v/>
       </c>
-      <c r="F28" s="20">
-        <f>SUM(F26:F27)</f>
+      <c r="F29" s="20">
+        <f>SUM(F27:F28)</f>
         <v/>
       </c>
-      <c r="G28" s="20">
-        <f>SUM(G26:G27)</f>
+      <c r="G29" s="20">
+        <f>SUM(G27:G28)</f>
         <v/>
       </c>
-      <c r="H28" s="20">
-        <f>SUM(H26:H27)</f>
+      <c r="H29" s="20">
+        <f>SUM(H27:H28)</f>
         <v/>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -1128,12 +1169,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="63.5" customWidth="1" min="1" max="1"/>
     <col width="41.5" customWidth="1" min="2" max="2"/>
-    <col width="22.5" customWidth="1" min="3" max="3"/>
+    <col width="41.5" customWidth="1" min="3" max="3"/>
     <col width="13.5" customWidth="1" min="4" max="4"/>
     <col width="18.5" customWidth="1" min="5" max="5"/>
     <col width="17.5" customWidth="1" min="6" max="6"/>
@@ -1228,140 +1269,140 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-1</t>
+          <t>P1-AP-1-1</t>
         </is>
       </c>
       <c r="E4" s="29" t="n">
-        <v>264.6</v>
+        <v>4850.7</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>211.7</v>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>265 × 212 mm</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>4851 × 1499 mm</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>0.056</v>
+        <v>7.2727</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>0.056</v>
+        <v>7.2727</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>952.5</v>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Standard Wall Panel</t>
-        </is>
-      </c>
-      <c r="N4" s="26" t="inlineStr">
+        <v>12700.01</v>
+      </c>
+      <c r="M4" s="28" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N4" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-2</t>
+          <t>P1-AP-1-2</t>
         </is>
       </c>
       <c r="E5" s="31" t="n">
-        <v>1234.7</v>
+        <v>1000.1</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>1235 × 794 mm</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>1000 × 106 mm</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>0.9801</v>
+        <v>0.1058</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>0.9801</v>
+        <v>0.1058</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>4056.95</v>
-      </c>
-      <c r="M5" s="28" t="inlineStr">
-        <is>
-          <t>Standard Wall Panel</t>
-        </is>
-      </c>
-      <c r="N5" s="28" t="inlineStr">
+        <v>2211.92</v>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>Acoustic Baffle / Slat</t>
+        </is>
+      </c>
+      <c r="N5" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-3</t>
+          <t>P1-AP-1-3</t>
         </is>
       </c>
       <c r="E6" s="29" t="n">
@@ -1370,12 +1411,12 @@
       <c r="F6" s="29" t="n">
         <v>793.8</v>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>1235 × 794 mm</t>
         </is>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="30" t="n">
@@ -1390,36 +1431,36 @@
       <c r="L6" s="29" t="n">
         <v>4056.95</v>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-4</t>
+          <t>P1-AP-1-4</t>
         </is>
       </c>
       <c r="E7" s="31" t="n">
@@ -1428,12 +1469,12 @@
       <c r="F7" s="31" t="n">
         <v>793.8</v>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>1235 × 794 mm</t>
         </is>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="32" t="n">
@@ -1448,36 +1489,36 @@
       <c r="L7" s="31" t="n">
         <v>4056.95</v>
       </c>
-      <c r="M7" s="28" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N7" s="28" t="inlineStr">
+      <c r="N7" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-5</t>
+          <t>P1-AP-1-5</t>
         </is>
       </c>
       <c r="E8" s="29" t="n">
@@ -1486,12 +1527,12 @@
       <c r="F8" s="29" t="n">
         <v>793.8</v>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>1235 × 794 mm</t>
         </is>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="30" t="n">
@@ -1506,94 +1547,94 @@
       <c r="L8" s="29" t="n">
         <v>4056.95</v>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N8" s="26" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-6</t>
+          <t>P1-AP-1-6</t>
         </is>
       </c>
       <c r="E9" s="31" t="n">
-        <v>1499.3</v>
+        <v>1234.7</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="G9" s="27" t="inlineStr">
-        <is>
-          <t>1499 × 882 mm</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>1235 × 794 mm</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>1.3223</v>
+        <v>0.9801</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>1.3223</v>
+        <v>0.9801</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>4762.5</v>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
+        <v>4056.95</v>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N9" s="28" t="inlineStr">
+      <c r="N9" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-7</t>
+          <t>P1-AP-1-7</t>
         </is>
       </c>
       <c r="E10" s="29" t="n">
@@ -1602,12 +1643,12 @@
       <c r="F10" s="29" t="n">
         <v>881.9</v>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>1499 × 882 mm</t>
         </is>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="30" t="n">
@@ -1622,36 +1663,36 @@
       <c r="L10" s="29" t="n">
         <v>4762.5</v>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N10" s="26" t="inlineStr">
+      <c r="N10" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-8</t>
+          <t>P1-AP-1-8</t>
         </is>
       </c>
       <c r="E11" s="31" t="n">
@@ -1660,12 +1701,12 @@
       <c r="F11" s="31" t="n">
         <v>881.9</v>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>1499 × 882 mm</t>
         </is>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="32" t="n">
@@ -1680,210 +1721,210 @@
       <c r="L11" s="31" t="n">
         <v>4762.5</v>
       </c>
-      <c r="M11" s="28" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N11" s="28" t="inlineStr">
+      <c r="N11" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-9</t>
+          <t>P1-AP-1-9</t>
         </is>
       </c>
       <c r="E12" s="29" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>1499 × 882 mm</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>1.3223</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>1.3223</v>
+      </c>
+      <c r="L12" s="29" t="n">
+        <v>4762.5</v>
+      </c>
+      <c r="M12" s="28" t="inlineStr">
+        <is>
+          <t>Standard Wall Panel</t>
+        </is>
+      </c>
+      <c r="N12" s="28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>P1-AP-1-10</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="n">
         <v>2293.1</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="G12" s="25" t="inlineStr">
-        <is>
-          <t>2293 × 706 mm</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="30" t="n">
-        <v>1.6179</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>1.6179</v>
-      </c>
-      <c r="L12" s="29" t="n">
-        <v>5997.23</v>
-      </c>
-      <c r="M12" s="26" t="inlineStr">
-        <is>
-          <t>Ceiling Cloud / Large Panel</t>
-        </is>
-      </c>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>P1-POLY-10</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>2116.7</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>705.6</v>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>2293 × 706 mm</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>1.6179</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>1.6179</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <v>5997.23</v>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N13" s="26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>P1-AP-1-11</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>2116.7</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>2117 × 706 mm</t>
         </is>
       </c>
-      <c r="H13" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32" t="n">
+      <c r="H14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
         <v>1.4934</v>
       </c>
-      <c r="K13" s="32" t="n">
+      <c r="K14" s="30" t="n">
         <v>1.4934</v>
       </c>
-      <c r="L13" s="31" t="n">
+      <c r="L14" s="29" t="n">
         <v>5644.45</v>
       </c>
-      <c r="M13" s="28" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N13" s="28" t="inlineStr">
+      <c r="N14" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>P1-POLY-11</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="G14" s="25" t="inlineStr">
-        <is>
-          <t>970 × 970 mm</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>0.9412</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>0.9412</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>3880.56</v>
-      </c>
-      <c r="M14" s="26" t="inlineStr">
-        <is>
-          <t>Standard Wall Panel</t>
-        </is>
-      </c>
-      <c r="N14" s="26" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-12</t>
+          <t>P1-AP-1-12</t>
         </is>
       </c>
       <c r="E15" s="31" t="n">
@@ -1892,12 +1933,12 @@
       <c r="F15" s="31" t="n">
         <v>970.1</v>
       </c>
-      <c r="G15" s="27" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>970 × 970 mm</t>
         </is>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="32" t="n">
@@ -1912,36 +1953,36 @@
       <c r="L15" s="31" t="n">
         <v>3880.56</v>
       </c>
-      <c r="M15" s="28" t="inlineStr">
+      <c r="M15" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N15" s="28" t="inlineStr">
+      <c r="N15" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>P1-POLY-13</t>
+          <t>P1-AP-1-13</t>
         </is>
       </c>
       <c r="E16" s="29" t="n">
@@ -1950,12 +1991,12 @@
       <c r="F16" s="29" t="n">
         <v>970.1</v>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>970 × 970 mm</t>
         </is>
       </c>
-      <c r="H16" s="25" t="n">
+      <c r="H16" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="30" t="n">
@@ -1970,36 +2011,36 @@
       <c r="L16" s="29" t="n">
         <v>3880.56</v>
       </c>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="M16" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N16" s="26" t="inlineStr">
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>P1-POLY-14</t>
+          <t>P1-AP-1-14</t>
         </is>
       </c>
       <c r="E17" s="31" t="n">
@@ -2008,12 +2049,12 @@
       <c r="F17" s="31" t="n">
         <v>970.1</v>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>970 × 970 mm</t>
         </is>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="32" t="n">
@@ -2028,94 +2069,94 @@
       <c r="L17" s="31" t="n">
         <v>3880.56</v>
       </c>
-      <c r="M17" s="28" t="inlineStr">
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N17" s="28" t="inlineStr">
+      <c r="N17" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>P1-WOOD-15</t>
+          <t>P1-AP-1-15</t>
         </is>
       </c>
       <c r="E18" s="29" t="n">
-        <v>264.6</v>
+        <v>970.1</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>211.7</v>
-      </c>
-      <c r="G18" s="25" t="inlineStr">
-        <is>
-          <t>265 × 212 mm</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>970 × 970 mm</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>0.056</v>
+        <v>0.9412</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>0.056</v>
+        <v>0.9412</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>952.5</v>
-      </c>
-      <c r="M18" s="26" t="inlineStr">
+        <v>3880.56</v>
+      </c>
+      <c r="M18" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N18" s="26" t="inlineStr">
+      <c r="N18" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>P1-WOOD-16</t>
+          <t>P1-AC-2-16</t>
         </is>
       </c>
       <c r="E19" s="31" t="n">
@@ -2124,12 +2165,12 @@
       <c r="F19" s="31" t="n">
         <v>1587.5</v>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G19" s="25" t="inlineStr">
         <is>
           <t>3881 × 1588 mm</t>
         </is>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="32" t="n">
@@ -2144,36 +2185,36 @@
       <c r="L19" s="31" t="n">
         <v>10936.12</v>
       </c>
-      <c r="M19" s="28" t="inlineStr">
+      <c r="M19" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N19" s="28" t="inlineStr">
+      <c r="N19" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>P1-WOOD-17</t>
+          <t>P1-AC-2-17</t>
         </is>
       </c>
       <c r="E20" s="29" t="n">
@@ -2182,12 +2223,12 @@
       <c r="F20" s="29" t="n">
         <v>1940.3</v>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>3881 × 1940 mm</t>
         </is>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="30" t="n">
@@ -2202,36 +2243,36 @@
       <c r="L20" s="29" t="n">
         <v>14816.68</v>
       </c>
-      <c r="M20" s="26" t="inlineStr">
+      <c r="M20" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N20" s="26" t="inlineStr">
+      <c r="N20" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>P1-WOOD-18</t>
+          <t>P1-AC-2-18</t>
         </is>
       </c>
       <c r="E21" s="31" t="n">
@@ -2240,12 +2281,12 @@
       <c r="F21" s="31" t="n">
         <v>881.9</v>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G21" s="25" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="32" t="n">
@@ -2260,36 +2301,36 @@
       <c r="L21" s="31" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M21" s="28" t="inlineStr">
+      <c r="M21" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N21" s="28" t="inlineStr">
+      <c r="N21" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>P1-WOOD-19</t>
+          <t>P1-AC-2-19</t>
         </is>
       </c>
       <c r="E22" s="29" t="n">
@@ -2298,12 +2339,12 @@
       <c r="F22" s="29" t="n">
         <v>881.9</v>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H22" s="25" t="n">
+      <c r="H22" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="30" t="n">
@@ -2318,36 +2359,36 @@
       <c r="L22" s="29" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M22" s="26" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N22" s="26" t="inlineStr">
+      <c r="N22" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>P1-WOOD-20</t>
+          <t>P1-AC-2-20</t>
         </is>
       </c>
       <c r="E23" s="31" t="n">
@@ -2356,12 +2397,12 @@
       <c r="F23" s="31" t="n">
         <v>881.9</v>
       </c>
-      <c r="G23" s="27" t="inlineStr">
+      <c r="G23" s="25" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="32" t="n">
@@ -2376,36 +2417,36 @@
       <c r="L23" s="31" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M23" s="28" t="inlineStr">
+      <c r="M23" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N23" s="28" t="inlineStr">
+      <c r="N23" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>P1-WOOD-21</t>
+          <t>P1-AC-2-21</t>
         </is>
       </c>
       <c r="E24" s="29" t="n">
@@ -2414,12 +2455,12 @@
       <c r="F24" s="29" t="n">
         <v>881.9</v>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="30" t="n">
@@ -2434,36 +2475,36 @@
       <c r="L24" s="29" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="M24" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N24" s="26" t="inlineStr">
+      <c r="N24" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>P1-WOOD-22</t>
+          <t>P1-AC-2-22</t>
         </is>
       </c>
       <c r="E25" s="31" t="n">
@@ -2472,12 +2513,12 @@
       <c r="F25" s="31" t="n">
         <v>881.9</v>
       </c>
-      <c r="G25" s="27" t="inlineStr">
+      <c r="G25" s="25" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="32" t="n">
@@ -2492,36 +2533,36 @@
       <c r="L25" s="31" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M25" s="28" t="inlineStr">
+      <c r="M25" s="26" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N25" s="28" t="inlineStr">
+      <c r="N25" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>P1-WOOD-23</t>
+          <t>P1-AC-2-23</t>
         </is>
       </c>
       <c r="E26" s="29" t="n">
@@ -2530,12 +2571,12 @@
       <c r="F26" s="29" t="n">
         <v>881.9</v>
       </c>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>1235 × 882 mm</t>
         </is>
       </c>
-      <c r="H26" s="25" t="n">
+      <c r="H26" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="30" t="n">
@@ -2550,26 +2591,26 @@
       <c r="L26" s="29" t="n">
         <v>4233.34</v>
       </c>
-      <c r="M26" s="26" t="inlineStr">
+      <c r="M26" s="28" t="inlineStr">
         <is>
           <t>Standard Wall Panel</t>
         </is>
       </c>
-      <c r="N26" s="26" t="inlineStr">
+      <c r="N26" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2579,55 +2620,55 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>P3-POLY-24</t>
+          <t>P1-POLY-24</t>
         </is>
       </c>
       <c r="E27" s="31" t="n">
-        <v>1411.1</v>
+        <v>1058.3</v>
       </c>
       <c r="F27" s="31" t="n">
         <v>1058.3</v>
       </c>
-      <c r="G27" s="27" t="inlineStr">
-        <is>
-          <t>1411 × 1058 mm</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>1058 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>1.4934</v>
+        <v>1.1201</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>1.4934</v>
+        <v>1.1201</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>4938.89</v>
-      </c>
-      <c r="M27" s="28" t="inlineStr">
+        <v>4233.34</v>
+      </c>
+      <c r="M27" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N27" s="28" t="inlineStr">
+      <c r="N27" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -2637,239 +2678,239 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>P3-POLY-25</t>
+          <t>P1-POLY-25</t>
         </is>
       </c>
       <c r="E28" s="29" t="n">
-        <v>1411.1</v>
+        <v>1058.3</v>
       </c>
       <c r="F28" s="29" t="n">
         <v>1058.3</v>
       </c>
-      <c r="G28" s="25" t="inlineStr">
-        <is>
-          <t>1411 × 1058 mm</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="n">
+      <c r="G28" s="27" t="inlineStr">
+        <is>
+          <t>1058 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>1.4934</v>
+        <v>1.1201</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>1.4934</v>
+        <v>1.1201</v>
       </c>
       <c r="L28" s="29" t="n">
-        <v>4938.89</v>
-      </c>
-      <c r="M28" s="26" t="inlineStr">
+        <v>4233.34</v>
+      </c>
+      <c r="M28" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N28" s="26" t="inlineStr">
+      <c r="N28" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Wood Slat Panel</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>P1-WOOD-26</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>1763.9</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>1764 × 494 mm</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="32" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="K29" s="32" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="L29" s="31" t="n">
+        <v>4515.56</v>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>Acoustic Baffle / Slat</t>
+        </is>
+      </c>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Wood Slat Panel</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>P1-WOOD-27</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>1763.9</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="G30" s="27" t="inlineStr">
+        <is>
+          <t>1764 × 494 mm</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="30" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="K30" s="30" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="L30" s="29" t="n">
+        <v>4515.56</v>
+      </c>
+      <c r="M30" s="28" t="inlineStr">
+        <is>
+          <t>Acoustic Baffle / Slat</t>
+        </is>
+      </c>
+      <c r="N30" s="28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>P3-POLY-26</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="F29" s="31" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="G29" s="27" t="inlineStr">
-        <is>
-          <t>1411 × 1058 mm</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="32" t="n">
-        <v>0.3236</v>
-      </c>
-      <c r="J29" s="32" t="n">
-        <v>1.4934</v>
-      </c>
-      <c r="K29" s="32" t="n">
-        <v>1.1699</v>
-      </c>
-      <c r="L29" s="31" t="n">
-        <v>4938.89</v>
-      </c>
-      <c r="M29" s="28" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>P3-AP-1-28</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>4850.7</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>4851 × 1499 mm</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="32" t="n">
+        <v>7.2727</v>
+      </c>
+      <c r="K31" s="32" t="n">
+        <v>7.2727</v>
+      </c>
+      <c r="L31" s="31" t="n">
+        <v>12700.01</v>
+      </c>
+      <c r="M31" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N29" s="28" t="inlineStr">
+      <c r="N31" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>P3-POLY-27</t>
-        </is>
-      </c>
-      <c r="E30" s="29" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="G30" s="25" t="inlineStr">
-        <is>
-          <t>1411 × 1058 mm</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="J30" s="30" t="n">
-        <v>1.4934</v>
-      </c>
-      <c r="K30" s="30" t="n">
-        <v>1.0454</v>
-      </c>
-      <c r="L30" s="29" t="n">
-        <v>4938.89</v>
-      </c>
-      <c r="M30" s="26" t="inlineStr">
-        <is>
-          <t>Ceiling Cloud / Large Panel</t>
-        </is>
-      </c>
-      <c r="N30" s="26" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>P3-POLY-28</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="F31" s="31" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="G31" s="27" t="inlineStr">
-        <is>
-          <t>1411 × 1058 mm</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="32" t="n">
-        <v>1.4934</v>
-      </c>
-      <c r="K31" s="32" t="n">
-        <v>1.4934</v>
-      </c>
-      <c r="L31" s="31" t="n">
-        <v>4938.89</v>
-      </c>
-      <c r="M31" s="28" t="inlineStr">
-        <is>
-          <t>Ceiling Cloud / Large Panel</t>
-        </is>
-      </c>
-      <c r="N31" s="28" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Polyester 9mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>P3-POLY-29</t>
+          <t>P3-AP-1-29</t>
         </is>
       </c>
       <c r="E32" s="29" t="n">
@@ -2878,12 +2919,12 @@
       <c r="F32" s="29" t="n">
         <v>1058.3</v>
       </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="G32" s="27" t="inlineStr">
         <is>
           <t>1411 × 1058 mm</t>
         </is>
       </c>
-      <c r="H32" s="25" t="n">
+      <c r="H32" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="30" t="n">
@@ -2898,384 +2939,384 @@
       <c r="L32" s="29" t="n">
         <v>4938.89</v>
       </c>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="M32" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N32" s="26" t="inlineStr">
+      <c r="N32" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>P3-WOOD-30</t>
+          <t>P3-AP-1-30</t>
         </is>
       </c>
       <c r="E33" s="31" t="n">
-        <v>1499.3</v>
+        <v>1411.1</v>
       </c>
       <c r="F33" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G33" s="27" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>1411 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M33" s="28" t="inlineStr">
+        <v>4938.89</v>
+      </c>
+      <c r="M33" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N33" s="28" t="inlineStr">
+      <c r="N33" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>P3-WOOD-31</t>
+          <t>P3-AP-1-31</t>
         </is>
       </c>
       <c r="E34" s="29" t="n">
-        <v>1499.3</v>
+        <v>1411.1</v>
       </c>
       <c r="F34" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="n">
-        <v>0</v>
+        <v>1058.3</v>
+      </c>
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>1411 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>0</v>
+        <v>0.3236</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>1.8512</v>
+        <v>1.1699</v>
       </c>
       <c r="L34" s="29" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M34" s="26" t="inlineStr">
+        <v>4938.89</v>
+      </c>
+      <c r="M34" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N34" s="26" t="inlineStr">
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B35" s="28" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>P3-WOOD-32</t>
+          <t>P3-AP-1-32</t>
         </is>
       </c>
       <c r="E35" s="31" t="n">
-        <v>1499.3</v>
+        <v>1411.1</v>
       </c>
       <c r="F35" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G35" s="27" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>0</v>
+        <v>1058.3</v>
+      </c>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>1411 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="32" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.0454</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M35" s="28" t="inlineStr">
+        <v>4938.89</v>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N35" s="28" t="inlineStr">
+      <c r="N35" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>P3-WOOD-33</t>
+          <t>P3-AP-1-33</t>
         </is>
       </c>
       <c r="E36" s="29" t="n">
-        <v>1499.3</v>
+        <v>1411.1</v>
       </c>
       <c r="F36" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="G36" s="27" t="inlineStr">
+        <is>
+          <t>1411 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="L36" s="29" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M36" s="26" t="inlineStr">
+        <v>4938.89</v>
+      </c>
+      <c r="M36" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N36" s="26" t="inlineStr">
+      <c r="N36" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>P3-WOOD-34</t>
+          <t>P3-AP-1-34</t>
         </is>
       </c>
       <c r="E37" s="31" t="n">
-        <v>1499.3</v>
+        <v>1411.1</v>
       </c>
       <c r="F37" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G37" s="27" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>1411 × 1058 mm</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="K37" s="32" t="n">
-        <v>1.8512</v>
+        <v>1.4934</v>
       </c>
       <c r="L37" s="31" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M37" s="28" t="inlineStr">
+        <v>4938.89</v>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N37" s="28" t="inlineStr">
+      <c r="N37" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Wood Slat Panel</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>P3-WOOD-35</t>
+          <t>P3-AP-1-35</t>
         </is>
       </c>
       <c r="E38" s="29" t="n">
-        <v>1499.3</v>
+        <v>1852.1</v>
       </c>
       <c r="F38" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="G38" s="25" t="inlineStr">
-        <is>
-          <t>1499 × 1235 mm</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="n">
+        <v>1146.5</v>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>1852 × 1146 mm</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>1.8512</v>
+        <v>2.1235</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>1.8512</v>
+        <v>2.1235</v>
       </c>
       <c r="L38" s="29" t="n">
-        <v>5468.06</v>
-      </c>
-      <c r="M38" s="26" t="inlineStr">
+        <v>5997.23</v>
+      </c>
+      <c r="M38" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N38" s="26" t="inlineStr">
+      <c r="N38" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Fabric Wrapped 25mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>P3-FABR-36</t>
+          <t>P3-AP-1-36</t>
         </is>
       </c>
       <c r="E39" s="31" t="n">
@@ -3284,12 +3325,12 @@
       <c r="F39" s="31" t="n">
         <v>1146.5</v>
       </c>
-      <c r="G39" s="27" t="inlineStr">
+      <c r="G39" s="25" t="inlineStr">
         <is>
           <t>1852 × 1146 mm</t>
         </is>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="32" t="n">
@@ -3304,36 +3345,36 @@
       <c r="L39" s="31" t="n">
         <v>5997.23</v>
       </c>
-      <c r="M39" s="28" t="inlineStr">
+      <c r="M39" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N39" s="28" t="inlineStr">
+      <c r="N39" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabric Wrapped 25mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>P3-FABR-37</t>
+          <t>P3-AP-1-37</t>
         </is>
       </c>
       <c r="E40" s="29" t="n">
@@ -3342,12 +3383,12 @@
       <c r="F40" s="29" t="n">
         <v>1146.5</v>
       </c>
-      <c r="G40" s="25" t="inlineStr">
+      <c r="G40" s="27" t="inlineStr">
         <is>
           <t>1852 × 1146 mm</t>
         </is>
       </c>
-      <c r="H40" s="25" t="n">
+      <c r="H40" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="30" t="n">
@@ -3362,36 +3403,36 @@
       <c r="L40" s="29" t="n">
         <v>5997.23</v>
       </c>
-      <c r="M40" s="26" t="inlineStr">
+      <c r="M40" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N40" s="26" t="inlineStr">
+      <c r="N40" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Fabric Wrapped 25mm</t>
+          <t>AP-1: Polyester 9mm Acoustic Panel</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>P3-FABR-38</t>
+          <t>P3-AP-1-38</t>
         </is>
       </c>
       <c r="E41" s="31" t="n">
@@ -3400,12 +3441,12 @@
       <c r="F41" s="31" t="n">
         <v>1146.5</v>
       </c>
-      <c r="G41" s="27" t="inlineStr">
+      <c r="G41" s="25" t="inlineStr">
         <is>
           <t>1852 × 1146 mm</t>
         </is>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="32" t="n">
@@ -3420,137 +3461,427 @@
       <c r="L41" s="31" t="n">
         <v>5997.23</v>
       </c>
-      <c r="M41" s="28" t="inlineStr">
+      <c r="M41" s="26" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N41" s="28" t="inlineStr">
+      <c r="N41" s="26" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Fabric Wrapped 25mm</t>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>P3-FABR-39</t>
+          <t>P3-AC-2-39</t>
         </is>
       </c>
       <c r="E42" s="29" t="n">
-        <v>1852.1</v>
+        <v>1499.3</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>1146.5</v>
-      </c>
-      <c r="G42" s="25" t="inlineStr">
-        <is>
-          <t>1852 × 1146 mm</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G42" s="27" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>2.1235</v>
+        <v>1.8512</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>2.1235</v>
+        <v>1.8512</v>
       </c>
       <c r="L42" s="29" t="n">
-        <v>5997.23</v>
-      </c>
-      <c r="M42" s="26" t="inlineStr">
+        <v>5468.06</v>
+      </c>
+      <c r="M42" s="28" t="inlineStr">
         <is>
           <t>Ceiling Cloud / Large Panel</t>
         </is>
       </c>
-      <c r="N42" s="26" t="inlineStr">
+      <c r="N42" s="28" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>P3-AC-2-40</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F43" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="K43" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="L43" s="31" t="n">
+        <v>5468.06</v>
+      </c>
+      <c r="M43" s="26" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N43" s="26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>P3-AC-2-41</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F44" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="30" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="L44" s="29" t="n">
+        <v>5468.06</v>
+      </c>
+      <c r="M44" s="28" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N44" s="28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>P3-AC-2-42</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F45" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="K45" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="L45" s="31" t="n">
+        <v>5468.06</v>
+      </c>
+      <c r="M45" s="26" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N45" s="26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>P3-AC-2-43</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F46" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G46" s="27" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="30" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="L46" s="29" t="n">
+        <v>5468.06</v>
+      </c>
+      <c r="M46" s="28" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N46" s="28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>P3-AC-2-44</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="F47" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="G47" s="25" t="inlineStr">
+        <is>
+          <t>1499 × 1235 mm</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="K47" s="32" t="n">
+        <v>1.8512</v>
+      </c>
+      <c r="L47" s="31" t="n">
+        <v>5468.06</v>
+      </c>
+      <c r="M47" s="26" t="inlineStr">
+        <is>
+          <t>Ceiling Cloud / Large Panel</t>
+        </is>
+      </c>
+      <c r="N47" s="26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>39 Panels</t>
-        </is>
-      </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>44 Panels</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="G48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="19">
-        <f>SUM(H4:H42)</f>
+      <c r="H48" s="19">
+        <f>SUM(H4:H47)</f>
         <v/>
       </c>
-      <c r="I43" s="33">
-        <f>SUM(I4:I42)</f>
+      <c r="I48" s="33">
+        <f>SUM(I4:I47)</f>
         <v/>
       </c>
-      <c r="J43" s="33">
-        <f>SUM(J4:J42)</f>
+      <c r="J48" s="33">
+        <f>SUM(J4:J47)</f>
         <v/>
       </c>
-      <c r="K43" s="33">
-        <f>SUM(K4:K42)</f>
+      <c r="K48" s="33">
+        <f>SUM(K4:K47)</f>
         <v/>
       </c>
-      <c r="L43" s="34">
-        <f>SUM(L4:L42)</f>
+      <c r="L48" s="34">
+        <f>SUM(L4:L47)</f>
         <v/>
       </c>
-      <c r="M43" s="22" t="inlineStr">
+      <c r="M48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N43" s="22" t="inlineStr">
+      <c r="N48" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3567,16 +3898,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="69.5" customWidth="1" min="1" max="1"/>
+    <col width="81.5" customWidth="1" min="1" max="1"/>
     <col width="18.5" customWidth="1" min="2" max="2"/>
     <col width="16.5" customWidth="1" min="3" max="3"/>
     <col width="41.5" customWidth="1" min="4" max="4"/>
     <col width="18.5" customWidth="1" min="5" max="5"/>
     <col width="22.5" customWidth="1" min="6" max="6"/>
-    <col width="21.5" customWidth="1" min="7" max="7"/>
+    <col width="22.5" customWidth="1" min="7" max="7"/>
     <col width="24.5" customWidth="1" min="8" max="8"/>
     <col width="15.5" customWidth="1" min="9" max="9"/>
   </cols>
@@ -3592,7 +3923,7 @@
     <row r="3">
       <c r="A3" s="35" t="inlineStr">
         <is>
-          <t>MATERIAL: FABRIC WRAPPED 25MM — NESTING CUT PLAN (4 SHEETS)</t>
+          <t>MATERIAL: AC-2: WOOD SLAT ACOUSTIC CEILING PANEL — NESTING CUT PLAN (6 SHEETS)</t>
         </is>
       </c>
     </row>
@@ -3649,34 +3980,34 @@
           <t>Sheet #1</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>2.123</v>
+        <v>1.089</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.7373000000000001</v>
+        <v>0.3781</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="H5" s="28" t="inlineStr">
-        <is>
-          <t>AP-036</t>
-        </is>
-      </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.6219</v>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>AP-018</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
@@ -3686,34 +4017,34 @@
           <t>Sheet #2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>2.123</v>
+        <v>1.089</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>0.7373000000000001</v>
+        <v>0.3781</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="H6" s="26" t="inlineStr">
-        <is>
-          <t>AP-037</t>
-        </is>
-      </c>
-      <c r="I6" s="25" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.6219</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>AP-019</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
@@ -3723,34 +4054,34 @@
           <t>Sheet #3</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>2.123</v>
+        <v>1.089</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.7373000000000001</v>
+        <v>0.3781</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="H7" s="28" t="inlineStr">
-        <is>
-          <t>AP-038</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.6219</v>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>AP-020</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
@@ -3760,231 +4091,227 @@
           <t>Sheet #4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>2.123</v>
+        <v>1.089</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.7373000000000001</v>
+        <v>0.3781</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>AP-039</t>
-        </is>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.6219</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>AP-021</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: Fabric Wrapped 25mm</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Sheet #5</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>AP-022</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #6</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>AP-023</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: AC-2: Wood Slat Acoustic Ceiling Panel</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="19">
-        <f>SUM(C5:C8)</f>
+      <c r="C11" s="19">
+        <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D9" s="33">
-        <f>SUM(D5:D8)</f>
+      <c r="D11" s="33">
+        <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="E9" s="33">
-        <f>SUM(E5:E8)</f>
+      <c r="E11" s="33">
+        <f>SUM(E5:E10)</f>
         <v/>
       </c>
-      <c r="F9" s="21">
-        <f>D9/E9</f>
+      <c r="F11" s="21">
+        <f>D11/E11</f>
         <v/>
       </c>
-      <c r="G9" s="21">
-        <f>1-F9</f>
+      <c r="G11" s="21">
+        <f>1-F11</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CNC SHOP CUTTING COORDINATES — FABRIC WRAPPED 25MM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>CNC SHOP CUTTING COORDINATES — AC-2: WOOD SLAT ACOUSTIC CEILING PANEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Sheet #</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Panel Tag</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Page No.</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>Room Name</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Cut X (mm)</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Cut Y (mm)</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>Length (mm)</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>Width (mm)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Rotated 90°</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Sheet #1</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>AP-036</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="31" t="n">
-        <v>1852.1</v>
-      </c>
-      <c r="H13" s="31" t="n">
-        <v>1146.5</v>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #2</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>AP-037</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>1852.1</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>1146.5</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #3</t>
-        </is>
-      </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>AP-038</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+          <t>AP-018</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="E15" s="31" t="n">
@@ -3994,36 +4321,36 @@
         <v>10</v>
       </c>
       <c r="G15" s="31" t="n">
-        <v>1852.1</v>
+        <v>1234.7</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>1146.5</v>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
+        <v>881.9</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #4</t>
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #2</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>AP-039</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+          <t>AP-019</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="E16" s="29" t="n">
@@ -4033,254 +4360,262 @@
         <v>10</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>1852.1</v>
+        <v>1234.7</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>1146.5</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
+        <v>881.9</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #3</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>AP-020</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #4</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>AP-021</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #5</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>AP-022</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>MATERIAL: POLYESTER 9MM — NESTING CUT PLAN (17 SHEETS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #6</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>AP-023</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H20" s="29" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>MATERIAL: AP-1: POLYESTER 9MM ACOUSTIC PANEL — NESTING CUT PLAN (21 SHEETS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Stock Sheet #</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Stock Size (mm)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Pieces Placed</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>Used Area (m²)</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>Sheet Area (m²)</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>Yield %</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>Waste %</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>Items Nested on Sheet</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>Origin Pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Sheet #1</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="30" t="n">
-        <v>1.618</v>
-      </c>
-      <c r="E22" s="30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>0.5618</v>
-      </c>
-      <c r="G22" s="17" t="n">
-        <v>0.4382</v>
-      </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>AP-009</t>
-        </is>
-      </c>
-      <c r="I22" s="25" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Sheet #2</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>1.494</v>
-      </c>
-      <c r="E23" s="32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0.5185999999999999</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0.4814</v>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>AP-010</t>
-        </is>
-      </c>
-      <c r="I23" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Sheet #3</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="30" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="E24" s="30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>0.4591</v>
-      </c>
-      <c r="G24" s="17" t="n">
-        <v>0.5409</v>
-      </c>
-      <c r="H24" s="26" t="inlineStr">
-        <is>
-          <t>AP-006</t>
-        </is>
-      </c>
-      <c r="I24" s="25" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Sheet #4</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="32" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="E25" s="32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0.4591</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0.5409</v>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>AP-007</t>
-        </is>
-      </c>
-      <c r="I25" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Sheet #5</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
+          <t>Sheet #1</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>1.322</v>
+        <v>1.618</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F26" s="17" t="n">
-        <v>0.4591</v>
+        <v>0.5618</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.5409</v>
-      </c>
-      <c r="H26" s="26" t="inlineStr">
-        <is>
-          <t>AP-008</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
+        <v>0.4382</v>
+      </c>
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>AP-010</t>
+        </is>
+      </c>
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
@@ -4289,72 +4624,72 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Sheet #6</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
+          <t>Sheet #2</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>1.493</v>
+        <v>1.494</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.5185</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>AP-024</t>
-        </is>
-      </c>
-      <c r="I27" s="27" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.4814</v>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>AP-011</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Sheet #7</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
+          <t>Sheet #3</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>1.493</v>
+        <v>2.123</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F28" s="17" t="n">
-        <v>0.5185</v>
+        <v>0.7373000000000001</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>AP-025</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="inlineStr">
+        <v>0.2627</v>
+      </c>
+      <c r="H28" s="28" t="inlineStr">
+        <is>
+          <t>AP-035</t>
+        </is>
+      </c>
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>P.3</t>
         </is>
@@ -4363,35 +4698,35 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Sheet #8</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
+          <t>Sheet #4</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>1.493</v>
+        <v>2.123</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.5185</v>
+        <v>0.7373000000000001</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>AP-026</t>
-        </is>
-      </c>
-      <c r="I29" s="27" t="inlineStr">
+        <v>0.2627</v>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>AP-036</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
         <is>
           <t>P.3</t>
         </is>
@@ -4400,35 +4735,35 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Sheet #9</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
+          <t>Sheet #5</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>1.493</v>
+        <v>2.123</v>
       </c>
       <c r="E30" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F30" s="17" t="n">
-        <v>0.5185</v>
+        <v>0.7373000000000001</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H30" s="26" t="inlineStr">
-        <is>
-          <t>AP-027</t>
-        </is>
-      </c>
-      <c r="I30" s="25" t="inlineStr">
+        <v>0.2627</v>
+      </c>
+      <c r="H30" s="28" t="inlineStr">
+        <is>
+          <t>AP-037</t>
+        </is>
+      </c>
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>P.3</t>
         </is>
@@ -4437,35 +4772,35 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Sheet #10</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
+          <t>Sheet #6</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>1.493</v>
+        <v>2.123</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.5185</v>
+        <v>0.7373000000000001</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>AP-028</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
+        <v>0.2627</v>
+      </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>AP-038</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
         <is>
           <t>P.3</t>
         </is>
@@ -4474,72 +4809,72 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Sheet #11</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
+          <t>Sheet #7</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>1.493</v>
+        <v>1.322</v>
       </c>
       <c r="E32" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F32" s="17" t="n">
-        <v>0.5185</v>
+        <v>0.4591</v>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>AP-029</t>
-        </is>
-      </c>
-      <c r="I32" s="25" t="inlineStr">
-        <is>
-          <t>P.3</t>
+        <v>0.5409</v>
+      </c>
+      <c r="H32" s="28" t="inlineStr">
+        <is>
+          <t>AP-007</t>
+        </is>
+      </c>
+      <c r="I32" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Sheet #12</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
+          <t>Sheet #8</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="32" t="n">
-        <v>0.98</v>
+        <v>1.322</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.3403</v>
+        <v>0.4591</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.6597</v>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
-        <is>
-          <t>AP-002</t>
-        </is>
-      </c>
-      <c r="I33" s="27" t="inlineStr">
+        <v>0.5409</v>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>AP-008</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
@@ -4548,35 +4883,35 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Sheet #13</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
+          <t>Sheet #9</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>0.98</v>
+        <v>1.322</v>
       </c>
       <c r="E34" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>0.3403</v>
+        <v>0.4591</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6597</v>
-      </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>AP-003</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="inlineStr">
+        <v>0.5409</v>
+      </c>
+      <c r="H34" s="28" t="inlineStr">
+        <is>
+          <t>AP-009</t>
+        </is>
+      </c>
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
@@ -4585,579 +4920,563 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Sheet #14</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
+          <t>Sheet #10</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="32" t="n">
-        <v>0.98</v>
+        <v>1.493</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.3403</v>
+        <v>0.5185</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.6597</v>
-      </c>
-      <c r="H35" s="28" t="inlineStr">
-        <is>
-          <t>AP-004</t>
-        </is>
-      </c>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
+        <v>0.4815</v>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>AP-029</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="inlineStr">
+        <is>
+          <t>P.3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Sheet #15</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
+          <t>Sheet #11</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C36" s="25" t="n">
-        <v>2</v>
+      <c r="C36" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="D36" s="30" t="n">
-        <v>1.921</v>
+        <v>1.493</v>
       </c>
       <c r="E36" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F36" s="17" t="n">
-        <v>0.6670999999999999</v>
+        <v>0.5185</v>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.3329</v>
-      </c>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>AP-005, AP-011</t>
-        </is>
-      </c>
-      <c r="I36" s="25" t="inlineStr">
-        <is>
-          <t>P.1</t>
+        <v>0.4815</v>
+      </c>
+      <c r="H36" s="28" t="inlineStr">
+        <is>
+          <t>AP-030</t>
+        </is>
+      </c>
+      <c r="I36" s="27" t="inlineStr">
+        <is>
+          <t>P.3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Sheet #16</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
+          <t>Sheet #12</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C37" s="27" t="n">
-        <v>2</v>
+      <c r="C37" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="D37" s="32" t="n">
-        <v>1.882</v>
+        <v>1.493</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>2.88</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.6535</v>
+        <v>0.5185</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3465</v>
-      </c>
-      <c r="H37" s="28" t="inlineStr">
-        <is>
-          <t>AP-012, AP-013</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
+        <v>0.4815</v>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>AP-031</t>
+        </is>
+      </c>
+      <c r="I37" s="25" t="inlineStr">
+        <is>
+          <t>P.3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Sheet #17</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="inlineStr">
+          <t>Sheet #13</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C38" s="25" t="n">
-        <v>2</v>
+      <c r="C38" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="D38" s="30" t="n">
-        <v>0.997</v>
+        <v>1.493</v>
       </c>
       <c r="E38" s="30" t="n">
         <v>2.88</v>
       </c>
       <c r="F38" s="17" t="n">
-        <v>0.3462</v>
+        <v>0.5185</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.6537999999999999</v>
-      </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>AP-014, AP-001</t>
-        </is>
-      </c>
-      <c r="I38" s="25" t="inlineStr">
+        <v>0.4815</v>
+      </c>
+      <c r="H38" s="28" t="inlineStr">
+        <is>
+          <t>AP-032</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="inlineStr">
+        <is>
+          <t>P.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Sheet #14</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="32" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="H39" s="26" t="inlineStr">
+        <is>
+          <t>AP-033</t>
+        </is>
+      </c>
+      <c r="I39" s="25" t="inlineStr">
+        <is>
+          <t>P.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #15</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>AP-034</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="inlineStr">
+        <is>
+          <t>P.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Sheet #16</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.6597</v>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>AP-003</t>
+        </is>
+      </c>
+      <c r="I41" s="25" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: Polyester 9mm</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #17</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>0.6597</v>
+      </c>
+      <c r="H42" s="28" t="inlineStr">
+        <is>
+          <t>AP-004</t>
+        </is>
+      </c>
+      <c r="I42" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Sheet #18</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E43" s="32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.6597</v>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>AP-005</t>
+        </is>
+      </c>
+      <c r="I43" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #19</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="H44" s="28" t="inlineStr">
+        <is>
+          <t>AP-006, AP-002</t>
+        </is>
+      </c>
+      <c r="I44" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Sheet #20</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>AP-012, AP-013</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #21</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>2400 × 1200</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="H46" s="28" t="inlineStr">
+        <is>
+          <t>AP-014, AP-015</t>
+        </is>
+      </c>
+      <c r="I46" s="27" t="inlineStr">
+        <is>
+          <t>P.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: AP-1: Polyester 9mm Acoustic Panel</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="19">
-        <f>SUM(C22:C38)</f>
+      <c r="C47" s="19">
+        <f>SUM(C26:C46)</f>
         <v/>
       </c>
-      <c r="D39" s="33">
-        <f>SUM(D22:D38)</f>
+      <c r="D47" s="33">
+        <f>SUM(D26:D46)</f>
         <v/>
       </c>
-      <c r="E39" s="33">
-        <f>SUM(E22:E38)</f>
+      <c r="E47" s="33">
+        <f>SUM(E26:E46)</f>
         <v/>
       </c>
-      <c r="F39" s="21">
-        <f>D39/E39</f>
+      <c r="F47" s="21">
+        <f>D47/E47</f>
         <v/>
       </c>
-      <c r="G39" s="21">
-        <f>1-F39</f>
+      <c r="G47" s="21">
+        <f>1-F47</f>
         <v/>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H47" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I47" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>CNC SHOP CUTTING COORDINATES — POLYESTER 9MM</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CNC SHOP CUTTING COORDINATES — AP-1: POLYESTER 9MM ACOUSTIC PANEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>Sheet #</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>Panel Tag</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>Page No.</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
         <is>
           <t>Room Name</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>Cut X (mm)</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>Cut Y (mm)</t>
         </is>
       </c>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="G50" s="24" t="inlineStr">
         <is>
           <t>Length (mm)</t>
         </is>
       </c>
-      <c r="H42" s="24" t="inlineStr">
+      <c r="H50" s="24" t="inlineStr">
         <is>
           <t>Width (mm)</t>
         </is>
       </c>
-      <c r="I42" s="24" t="inlineStr">
+      <c r="I50" s="24" t="inlineStr">
         <is>
           <t>Rotated 90°</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>Sheet #1</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>AP-009</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>AP-010</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D43" s="28" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E43" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F43" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" s="31" t="n">
-        <v>2293.1</v>
-      </c>
-      <c r="H43" s="31" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="I43" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #2</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>AP-010</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E44" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F44" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="29" t="n">
-        <v>2116.7</v>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="I44" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #3</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>AP-006</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E45" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F45" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" s="31" t="n">
-        <v>1499.3</v>
-      </c>
-      <c r="H45" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I45" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #4</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>AP-007</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E46" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G46" s="29" t="n">
-        <v>1499.3</v>
-      </c>
-      <c r="H46" s="29" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I46" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #5</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>AP-008</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F47" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G47" s="31" t="n">
-        <v>1499.3</v>
-      </c>
-      <c r="H47" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #6</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>AP-024</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="E48" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F48" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" s="29" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I48" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #7</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>AP-025</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G49" s="31" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="H49" s="31" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I49" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #8</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>AP-026</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
-        </is>
-      </c>
-      <c r="E50" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F50" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G50" s="29" t="n">
-        <v>1411.1</v>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I50" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #9</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>AP-027</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E51" s="31" t="n">
@@ -5167,36 +5486,36 @@
         <v>10</v>
       </c>
       <c r="G51" s="31" t="n">
-        <v>1411.1</v>
+        <v>2293.1</v>
       </c>
       <c r="H51" s="31" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I51" s="27" t="inlineStr">
+        <v>705.6</v>
+      </c>
+      <c r="I51" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #10</t>
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #2</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>AP-028</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+          <t>AP-011</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="E52" s="29" t="n">
@@ -5206,34 +5525,34 @@
         <v>10</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>1411.1</v>
+        <v>2116.7</v>
       </c>
       <c r="H52" s="29" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I52" s="25" t="inlineStr">
+        <v>705.6</v>
+      </c>
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #11</t>
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #3</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>AP-029</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
+          <t>AP-035</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
         <is>
           <t>Page 3</t>
         </is>
       </c>
-      <c r="D53" s="28" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
@@ -5245,36 +5564,36 @@
         <v>10</v>
       </c>
       <c r="G53" s="31" t="n">
-        <v>1411.1</v>
+        <v>1852.1</v>
       </c>
       <c r="H53" s="31" t="n">
-        <v>1058.3</v>
-      </c>
-      <c r="I53" s="27" t="inlineStr">
+        <v>1146.5</v>
+      </c>
+      <c r="I53" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #12</t>
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #4</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>AP-002</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-036</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E54" s="29" t="n">
@@ -5284,36 +5603,36 @@
         <v>10</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>1234.7</v>
+        <v>1852.1</v>
       </c>
       <c r="H54" s="29" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="I54" s="25" t="inlineStr">
+        <v>1146.5</v>
+      </c>
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #13</t>
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #5</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>AP-003</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D55" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-037</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E55" s="31" t="n">
@@ -5323,36 +5642,36 @@
         <v>10</v>
       </c>
       <c r="G55" s="31" t="n">
-        <v>1234.7</v>
+        <v>1852.1</v>
       </c>
       <c r="H55" s="31" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="I55" s="27" t="inlineStr">
+        <v>1146.5</v>
+      </c>
+      <c r="I55" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #14</t>
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #6</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>AP-004</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-038</t>
+        </is>
+      </c>
+      <c r="C56" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E56" s="29" t="n">
@@ -5362,34 +5681,34 @@
         <v>10</v>
       </c>
       <c r="G56" s="29" t="n">
-        <v>1234.7</v>
+        <v>1852.1</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="I56" s="25" t="inlineStr">
+        <v>1146.5</v>
+      </c>
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #15</t>
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #7</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>AP-005</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
+          <t>AP-007</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D57" s="28" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
@@ -5401,73 +5720,73 @@
         <v>10</v>
       </c>
       <c r="G57" s="31" t="n">
-        <v>1234.7</v>
+        <v>1499.3</v>
       </c>
       <c r="H57" s="31" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="I57" s="27" t="inlineStr">
+        <v>881.9</v>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #15</t>
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #8</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>AP-011</t>
-        </is>
-      </c>
-      <c r="C58" s="25" t="inlineStr">
+          <t>AP-008</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
       <c r="E58" s="29" t="n">
-        <v>1247.7</v>
+        <v>10</v>
       </c>
       <c r="F58" s="29" t="n">
         <v>10</v>
       </c>
       <c r="G58" s="29" t="n">
-        <v>970.1</v>
+        <v>1499.3</v>
       </c>
       <c r="H58" s="29" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="I58" s="25" t="inlineStr">
+        <v>881.9</v>
+      </c>
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #16</t>
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #9</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>AP-012</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
+          <t>AP-009</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D59" s="28" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
@@ -5479,75 +5798,75 @@
         <v>10</v>
       </c>
       <c r="G59" s="31" t="n">
-        <v>970.1</v>
+        <v>1499.3</v>
       </c>
       <c r="H59" s="31" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="I59" s="27" t="inlineStr">
+        <v>881.9</v>
+      </c>
+      <c r="I59" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #16</t>
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #10</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>AP-013</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D60" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-029</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D60" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E60" s="29" t="n">
-        <v>983.1</v>
+        <v>10</v>
       </c>
       <c r="F60" s="29" t="n">
         <v>10</v>
       </c>
       <c r="G60" s="29" t="n">
-        <v>970.1</v>
+        <v>1411.1</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="I60" s="25" t="inlineStr">
+        <v>1058.3</v>
+      </c>
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #17</t>
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #11</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>AP-014</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D61" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-030</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E61" s="31" t="n">
@@ -5557,711 +5876,1322 @@
         <v>10</v>
       </c>
       <c r="G61" s="31" t="n">
-        <v>970.1</v>
+        <v>1411.1</v>
       </c>
       <c r="H61" s="31" t="n">
-        <v>970.1</v>
-      </c>
-      <c r="I61" s="27" t="inlineStr">
+        <v>1058.3</v>
+      </c>
+      <c r="I61" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #17</t>
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #12</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>AP-001</t>
-        </is>
-      </c>
-      <c r="C62" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+          <t>AP-031</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
         </is>
       </c>
       <c r="E62" s="29" t="n">
-        <v>983.1</v>
+        <v>10</v>
       </c>
       <c r="F62" s="29" t="n">
         <v>10</v>
       </c>
       <c r="G62" s="29" t="n">
-        <v>264.6</v>
+        <v>1411.1</v>
       </c>
       <c r="H62" s="29" t="n">
-        <v>211.7</v>
-      </c>
-      <c r="I62" s="25" t="inlineStr">
+        <v>1058.3</v>
+      </c>
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
+    <row r="63">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #13</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>AP-032</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="E63" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G63" s="31" t="n">
+        <v>1411.1</v>
+      </c>
+      <c r="H63" s="31" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="I63" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #14</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>AP-033</t>
+        </is>
+      </c>
+      <c r="C64" s="27" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F64" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G64" s="29" t="n">
+        <v>1411.1</v>
+      </c>
+      <c r="H64" s="29" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="I64" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #15</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>AP-034</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>Page 3</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 5 AUDITORIUM ACOUSTIC TREATMENT</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F65" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" s="31" t="n">
+        <v>1411.1</v>
+      </c>
+      <c r="H65" s="31" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="I65" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="35" t="inlineStr">
-        <is>
-          <t>MATERIAL: WOOD SLAT PANEL — NESTING CUT PLAN (6 SHEETS)</t>
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #16</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>AP-003</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H66" s="29" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="I66" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #17</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>AP-004</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H67" s="31" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="I67" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #18</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>AP-005</t>
+        </is>
+      </c>
+      <c r="C68" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D68" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="29" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H68" s="29" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="I68" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #19</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>AP-006</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>1234.7</v>
+      </c>
+      <c r="H69" s="31" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="I69" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #19</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>AP-002</t>
+        </is>
+      </c>
+      <c r="C70" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D70" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="n">
+        <v>1247.7</v>
+      </c>
+      <c r="F70" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G70" s="29" t="n">
+        <v>1000.1</v>
+      </c>
+      <c r="H70" s="29" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="I70" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #20</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>AP-012</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="H71" s="31" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="I71" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #20</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>AP-013</t>
+        </is>
+      </c>
+      <c r="C72" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E72" s="29" t="n">
+        <v>983.1</v>
+      </c>
+      <c r="F72" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" s="29" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="H72" s="29" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="I72" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #21</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>AP-014</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="H73" s="31" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="I73" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #21</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>AP-015</t>
+        </is>
+      </c>
+      <c r="C74" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="n">
+        <v>983.1</v>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G74" s="29" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="H74" s="29" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="35" t="inlineStr">
+        <is>
+          <t>MATERIAL: POLYESTER 9MM — NESTING CUT PLAN (1 SHEETS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>Stock Sheet #</t>
         </is>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B79" s="24" t="inlineStr">
         <is>
           <t>Stock Size (mm)</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C79" s="24" t="inlineStr">
         <is>
           <t>Pieces Placed</t>
         </is>
       </c>
-      <c r="D67" s="24" t="inlineStr">
+      <c r="D79" s="24" t="inlineStr">
         <is>
           <t>Used Area (m²)</t>
         </is>
       </c>
-      <c r="E67" s="24" t="inlineStr">
+      <c r="E79" s="24" t="inlineStr">
         <is>
           <t>Sheet Area (m²)</t>
         </is>
       </c>
-      <c r="F67" s="24" t="inlineStr">
+      <c r="F79" s="24" t="inlineStr">
         <is>
           <t>Yield %</t>
         </is>
       </c>
-      <c r="G67" s="24" t="inlineStr">
+      <c r="G79" s="24" t="inlineStr">
         <is>
           <t>Waste %</t>
         </is>
       </c>
-      <c r="H67" s="24" t="inlineStr">
+      <c r="H79" s="24" t="inlineStr">
         <is>
           <t>Items Nested on Sheet</t>
         </is>
       </c>
-      <c r="I67" s="24" t="inlineStr">
+      <c r="I79" s="24" t="inlineStr">
         <is>
           <t>Origin Pages</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t>Sheet #1</t>
         </is>
       </c>
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C68" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="30" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E68" s="30" t="n">
+      <c r="C80" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E80" s="30" t="n">
         <v>2.88</v>
       </c>
-      <c r="F68" s="17" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="G68" s="17" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="H68" s="26" t="inlineStr">
-        <is>
-          <t>AP-018</t>
-        </is>
-      </c>
-      <c r="I68" s="25" t="inlineStr">
+      <c r="F80" s="17" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="G80" s="17" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="H80" s="28" t="inlineStr">
+        <is>
+          <t>AP-024, AP-025</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>Sheet #2</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: Polyester 9mm</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" s="19">
+        <f>SUM(C80:C80)</f>
+        <v/>
+      </c>
+      <c r="D81" s="33">
+        <f>SUM(D80:D80)</f>
+        <v/>
+      </c>
+      <c r="E81" s="33">
+        <f>SUM(E80:E80)</f>
+        <v/>
+      </c>
+      <c r="F81" s="21">
+        <f>D81/E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="21">
+        <f>1-F81</f>
+        <v/>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>CNC SHOP CUTTING COORDINATES — POLYESTER 9MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>Sheet #</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>Panel Tag</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>Page No.</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Room Name</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>Cut X (mm)</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Cut Y (mm)</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Length (mm)</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>Width (mm)</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>Rotated 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>Sheet #1</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>AP-024</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E85" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" s="31" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="H85" s="31" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="I85" s="25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #1</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>AP-025</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="inlineStr">
+        <is>
+          <t>Page 1</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="inlineStr">
+        <is>
+          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="n">
+        <v>1071.3</v>
+      </c>
+      <c r="F86" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" s="29" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="H86" s="29" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="35" t="inlineStr">
+        <is>
+          <t>MATERIAL: WOOD SLAT PANEL — NESTING CUT PLAN (1 SHEETS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>Stock Sheet #</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>Stock Size (mm)</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>Pieces Placed</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>Used Area (m²)</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Sheet Area (m²)</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>Yield %</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Waste %</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Items Nested on Sheet</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>Origin Pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>Sheet #1</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>2400 × 1200</t>
         </is>
       </c>
-      <c r="C69" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E69" s="32" t="n">
+      <c r="C92" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="30" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="E92" s="30" t="n">
         <v>2.88</v>
       </c>
-      <c r="F69" s="12" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="H69" s="28" t="inlineStr">
-        <is>
-          <t>AP-019</t>
-        </is>
-      </c>
-      <c r="I69" s="27" t="inlineStr">
+      <c r="F92" s="17" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H92" s="28" t="inlineStr">
+        <is>
+          <t>AP-026, AP-027</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
         <is>
           <t>P.1</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>Sheet #3</t>
-        </is>
-      </c>
-      <c r="B70" s="25" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C70" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="30" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E70" s="30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F70" s="17" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="G70" s="17" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="H70" s="26" t="inlineStr">
-        <is>
-          <t>AP-020</t>
-        </is>
-      </c>
-      <c r="I70" s="25" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>Sheet #4</t>
-        </is>
-      </c>
-      <c r="B71" s="27" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C71" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="H71" s="28" t="inlineStr">
-        <is>
-          <t>AP-021</t>
-        </is>
-      </c>
-      <c r="I71" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>Sheet #5</t>
-        </is>
-      </c>
-      <c r="B72" s="25" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C72" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="30" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E72" s="30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F72" s="17" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="G72" s="17" t="n">
-        <v>0.6219</v>
-      </c>
-      <c r="H72" s="26" t="inlineStr">
-        <is>
-          <t>AP-022</t>
-        </is>
-      </c>
-      <c r="I72" s="25" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>Sheet #6</t>
-        </is>
-      </c>
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>2400 × 1200</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>1.145</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>0.3975</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>0.6025</v>
-      </c>
-      <c r="H73" s="28" t="inlineStr">
-        <is>
-          <t>AP-023, AP-015</t>
-        </is>
-      </c>
-      <c r="I73" s="27" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr">
         <is>
           <t>SUBTOTAL: Wood Slat Panel</t>
         </is>
       </c>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B93" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="19">
-        <f>SUM(C68:C73)</f>
+      <c r="C93" s="19">
+        <f>SUM(C92:C92)</f>
         <v/>
       </c>
-      <c r="D74" s="33">
-        <f>SUM(D68:D73)</f>
+      <c r="D93" s="33">
+        <f>SUM(D92:D92)</f>
         <v/>
       </c>
-      <c r="E74" s="33">
-        <f>SUM(E68:E73)</f>
+      <c r="E93" s="33">
+        <f>SUM(E92:E92)</f>
         <v/>
       </c>
-      <c r="F74" s="21">
-        <f>D74/E74</f>
+      <c r="F93" s="21">
+        <f>D93/E93</f>
         <v/>
       </c>
-      <c r="G74" s="21">
-        <f>1-F74</f>
+      <c r="G93" s="21">
+        <f>1-F93</f>
         <v/>
       </c>
-      <c r="H74" s="22" t="inlineStr">
+      <c r="H93" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="22" t="inlineStr">
+      <c r="I93" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>CNC SHOP CUTTING COORDINATES — WOOD SLAT PANEL</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="24" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
         <is>
           <t>Sheet #</t>
         </is>
       </c>
-      <c r="B77" s="24" t="inlineStr">
+      <c r="B96" s="24" t="inlineStr">
         <is>
           <t>Panel Tag</t>
         </is>
       </c>
-      <c r="C77" s="24" t="inlineStr">
+      <c r="C96" s="24" t="inlineStr">
         <is>
           <t>Page No.</t>
         </is>
       </c>
-      <c r="D77" s="24" t="inlineStr">
+      <c r="D96" s="24" t="inlineStr">
         <is>
           <t>Room Name</t>
         </is>
       </c>
-      <c r="E77" s="24" t="inlineStr">
+      <c r="E96" s="24" t="inlineStr">
         <is>
           <t>Cut X (mm)</t>
         </is>
       </c>
-      <c r="F77" s="24" t="inlineStr">
+      <c r="F96" s="24" t="inlineStr">
         <is>
           <t>Cut Y (mm)</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
+      <c r="G96" s="24" t="inlineStr">
         <is>
           <t>Length (mm)</t>
         </is>
       </c>
-      <c r="H77" s="24" t="inlineStr">
+      <c r="H96" s="24" t="inlineStr">
         <is>
           <t>Width (mm)</t>
         </is>
       </c>
-      <c r="I77" s="24" t="inlineStr">
+      <c r="I96" s="24" t="inlineStr">
         <is>
           <t>Rotated 90°</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="25" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="25" t="inlineStr">
         <is>
           <t>Sheet #1</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>AP-018</t>
-        </is>
-      </c>
-      <c r="C78" s="25" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>AP-026</t>
+        </is>
+      </c>
+      <c r="C97" s="25" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="D97" s="26" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E97" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="F78" s="29" t="n">
+      <c r="F97" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G78" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H78" s="29" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I78" s="25" t="inlineStr">
+      <c r="G97" s="31" t="n">
+        <v>1763.9</v>
+      </c>
+      <c r="H97" s="31" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="I97" s="25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #2</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>AP-019</t>
-        </is>
-      </c>
-      <c r="C79" s="27" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>Sheet #1</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>AP-027</t>
+        </is>
+      </c>
+      <c r="C98" s="27" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>
       </c>
-      <c r="D79" s="28" t="inlineStr">
+      <c r="D98" s="28" t="inlineStr">
         <is>
           <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
         </is>
       </c>
-      <c r="E79" s="31" t="n">
+      <c r="E98" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="F79" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H79" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I79" s="27" t="inlineStr">
+      <c r="F98" s="29" t="n">
+        <v>506.9</v>
+      </c>
+      <c r="G98" s="29" t="n">
+        <v>1763.9</v>
+      </c>
+      <c r="H98" s="29" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="I98" s="27" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #3</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>AP-020</t>
-        </is>
-      </c>
-      <c r="C80" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D80" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E80" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F80" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G80" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H80" s="29" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I80" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #4</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>AP-021</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D81" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G81" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H81" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I81" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #5</t>
-        </is>
-      </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>AP-022</t>
-        </is>
-      </c>
-      <c r="C82" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E82" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F82" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G82" s="29" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H82" s="29" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I82" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>Sheet #6</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>AP-023</t>
-        </is>
-      </c>
-      <c r="C83" s="27" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D83" s="28" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>1234.7</v>
-      </c>
-      <c r="H83" s="31" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="I83" s="27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="25" t="inlineStr">
-        <is>
-          <t>Sheet #6</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>AP-015</t>
-        </is>
-      </c>
-      <c r="C84" s="25" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="inlineStr">
-        <is>
-          <t>LEVEL 4 ACOUSTIC WALL &amp; CEILING FITOUT</t>
-        </is>
-      </c>
-      <c r="E84" s="29" t="n">
-        <v>1247.7</v>
-      </c>
-      <c r="F84" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G84" s="29" t="n">
-        <v>264.6</v>
-      </c>
-      <c r="H84" s="29" t="n">
-        <v>211.7</v>
-      </c>
-      <c r="I84" s="25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A20:I20"/>
+  <mergeCells count="4">
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A78:I78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55.5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="3" max="3"/>
+    <col width="17.5" customWidth="1" min="4" max="4"/>
+    <col width="56.5" customWidth="1" min="5" max="5"/>
+    <col width="269.5" customWidth="1" min="6" max="6"/>
+    <col width="147.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTOR DRAFTING QUALITY CONTROL &amp; GEOMETRY AUDIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>Element Tag</t>
+        </is>
+      </c>
+      <c r="E3" s="36" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F3" s="36" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="G3" s="36" t="inlineStr">
+        <is>
+          <t>Remedy / Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>QC-GAP-01</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Unclosed Geometry</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Unclosed Line Chain (1015.4 mm Opening)</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>A chain of 3 connected CAD lines forms an open perimeter but stops short. The gap between line start (455.0, 380.0) and line end (472.0, 435.0) measures 57.6 pt (1015.4 mm). This perimeter cannot be converted to a solid panel.</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Auto-snap gap with 1020.4 mm tolerance or add missing CAD line segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>QC-DIM-01</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Fake Dimension</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>AP-012</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Dimension Text Override (59.6% Discrepancy on AP-012)</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Annotated dimension text specifies '2400 mm' near panel AP-012, but the underlying CAD vector geometry measures only 970.1 mm Width (Difference: 1429.9 mm, 59.6% error). The drafter manually overrode the dimension string without updating CAD geometry.</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Consult architect/contractor: if 2400.0 mm is required, adjust the cutting schedule or stretch the drawing geometry before material procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>QC-SCL-02</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Scale Conflict</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Conflicting Scales Detected on Page</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>Found multiple scale annotations on this page: 1:50, 1:100. Detail drawings or callouts may be drawn at a different scale from the general floor plan.</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Verify which sections of the drawing correspond to detail callouts to avoid applying the wrong scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>QC-DUP-01</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Duplicate Entity</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate Overlapping CAD Path (1235×882 mm)</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Vector paths #25 and #41 are drawn in the exact same coordinates (bbox: 480.0, 140.0). This commonly occurs when drafting elements are copied and pasted in place or duplicated across multiple CAD layers, causing double-counting in takeoff quantities if not filtered.</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Delete duplicate entity in CAD or verify that deduplication filter is enabled in takeoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>QC-DUP-02</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Duplicate Entity</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>AP-001, AP-028</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate Overlapping Panel (AP-001 &amp; AP-028)</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>Panel AP-001 and AP-028 share nearly identical positions (centroid distance: 0.0 mm, area diff: 0.0%).</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Delete duplicate instance or merge identical layers before nesting and takeoff.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>